--- a/Exemplo_old.xlsx
+++ b/Exemplo_old.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vera/Documents/GitHub/SEED/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2035A195-0327-7545-BF86-F9E50763CCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BBC8C6-B53B-394D-817B-1E3B59A81071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8860" yWindow="4300" windowWidth="19940" windowHeight="7680" xr2:uid="{2ACA29F8-B164-2441-8861-0B1619084B7B}"/>
   </bookViews>
@@ -47,18 +47,6 @@
     <t>condition_encode</t>
   </si>
   <si>
-    <t>Scenes_Dataset/movie_theater_A.jpg</t>
-  </si>
-  <si>
-    <t>(600,364)</t>
-  </si>
-  <si>
-    <t>Scenes_Dataset/museum_A.jpg</t>
-  </si>
-  <si>
-    <t>(600,337)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> old</t>
   </si>
   <si>
@@ -68,15 +56,6 @@
     <t>old</t>
   </si>
   <si>
-    <t>Scenes_Dataset/building_entrance_A.jpg</t>
-  </si>
-  <si>
-    <t>Scenes_Dataset/boat_interior_A.jpg</t>
-  </si>
-  <si>
-    <t>(600,400)</t>
-  </si>
-  <si>
     <t>ex_scene_old_new</t>
   </si>
   <si>
@@ -87,6 +66,27 @@
   </si>
   <si>
     <t>3.25</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/temple_A.jpg</t>
+  </si>
+  <si>
+    <t>(600,358)</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/athletics_track_A</t>
+  </si>
+  <si>
+    <t>(600,450)</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/sky_A.jpg</t>
+  </si>
+  <si>
+    <t>(600,398)</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/painting_workshop_A.jpg</t>
   </si>
 </sst>
 </file>
@@ -498,7 +498,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -507,7 +507,7 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -515,13 +515,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -532,13 +532,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
         <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
       </c>
       <c r="E3">
         <v>3</v>
@@ -552,13 +552,13 @@
         <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
         <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -566,16 +566,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Exemplo_old.xlsx
+++ b/Exemplo_old.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vera/Documents/GitHub/SEED/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BBC8C6-B53B-394D-817B-1E3B59A81071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D649E9-2E6E-B84E-B02E-93954480E5F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8860" yWindow="4300" windowWidth="19940" windowHeight="7680" xr2:uid="{2ACA29F8-B164-2441-8861-0B1619084B7B}"/>
+    <workbookView xWindow="14560" yWindow="1460" windowWidth="14240" windowHeight="10520" xr2:uid="{2ACA29F8-B164-2441-8861-0B1619084B7B}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>

--- a/Exemplo_old.xlsx
+++ b/Exemplo_old.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vera/Documents/GitHub/SEED/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BBC8C6-B53B-394D-817B-1E3B59A81071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF790888-A06C-7C48-820A-6CE58F75455F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8860" yWindow="4300" windowWidth="19940" windowHeight="7680" xr2:uid="{2ACA29F8-B164-2441-8861-0B1619084B7B}"/>
   </bookViews>
@@ -74,9 +74,6 @@
     <t>(600,358)</t>
   </si>
   <si>
-    <t>Scenes_Dataset/athletics_track_A</t>
-  </si>
-  <si>
     <t>(600,450)</t>
   </si>
   <si>
@@ -87,6 +84,9 @@
   </si>
   <si>
     <t>Scenes_Dataset/painting_workshop_A.jpg</t>
+  </si>
+  <si>
+    <t>Scenes_Dataset/athletics_track_A.jpg</t>
   </si>
 </sst>
 </file>
@@ -515,10 +515,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
@@ -532,10 +532,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -566,10 +566,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
